--- a/prompts/Contextual_Form_SOP.xlsx
+++ b/prompts/Contextual_Form_SOP.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/edgardomosesezekielaverilla/Documents/Documents - Edgardo’s MacBook Air/Projects/AiDA-Documentation-Agent/prompts/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51BCB853-C535-0E49-93AB-E9C1CF55FA4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82EC36AC-9282-864F-AA8A-C09E5E604801}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="20260" windowHeight="19260" xr2:uid="{E3E65FFB-6B3D-2846-B138-AECE72D99295}"/>
+    <workbookView xWindow="-22240" yWindow="600" windowWidth="22240" windowHeight="14800" xr2:uid="{E3E65FFB-6B3D-2846-B138-AECE72D99295}"/>
   </bookViews>
   <sheets>
     <sheet name="WI Context Form" sheetId="1" r:id="rId1"/>
@@ -53,9 +53,6 @@
     <t>Purpose</t>
   </si>
   <si>
-    <t>Prompt: "If provided, rephrase into 1-2 concise sentences. If blank, infer from Title and related SOP, then append: 'Review required: Purpose statement generated without user input.'"</t>
-  </si>
-  <si>
     <t>2. Scope</t>
   </si>
   <si>
@@ -63,13 +60,6 @@
   </si>
   <si>
     <t>Systems Involved</t>
-  </si>
-  <si>
-    <t>Prompt: If entries are present, list each team or region clearly. If blank, insert placeholder text: 'Team/region aplpicability pending confirmation by author.' Do not assume or generate department names."</t>
-  </si>
-  <si>
-    <t>Prompt "If system information is provided, structure into a two-column table ("System/Tool',
-*Purpose'). If not provided, infer likely systems based on [Process Name] context (e.g., CRM, Workday, ServiceNow), add short neutral descriptions, and append: A Review required: system list generated based on contextual inference.' Example output: \n</t>
   </si>
   <si>
     <t>Step No. + Action</t>
@@ -112,61 +102,111 @@
     <t>Escalation Matrix</t>
   </si>
   <si>
-    <t>Prompt: "If a process summary is provided, refine it into 1-2 concise, formal paragraphs summarizing the start, key stages, and conclusion of [Process Name]. Maintain neutral, instructional tone aligned with JLL SOP standards.
-If blank, infer a logical high-level outline based on the Title, Systems Involved, and Exclusions, and generate a placeholder summary. Append:
-*A Review required: process summary generated without direct user input.'
-Example placeholder: The process begins with [Step 1], progresses through [Step 2], and concludes with [Step 3]. A Review required: process summary generated without direct user input."</t>
-  </si>
-  <si>
-    <t>Prompt: "If steps are provided:
-* ﻿﻿For numerical input (1., 2., 3.), preserve numbering and clarify each step into a concise instruction.
-* ﻿﻿For descriptive input (paragraph style), convert to sequential numbered steps.
-Assign a Flowchart Shape to each step based on action type: Start/End → Terminator, Enter/Update → Process, Verify/Check → Decision,
-Create Document → Document,
-Input/Output → Data.
-Present results as a four-column table: Step No., Actib, Flowchart Shape, Notes.
-If blank, infer 3-7 logical steps from SOP context (Title, Systems) and assign shapes accordingly.
-Append:
-*A Review required: process flow generated using contextual inference.'
-Example output:
-| Step No. | Action | Flowchart Shape | Notes | | 1 | Start process | Terminator | Entry point for
-SOP procedure
-| 2 | Log in to CRM system | Process | Standard action/operation |
-| 3 | Enter client data | Process | Key operational step |
-| 4 | Verify data accuracy | Decision | Yes/No outcome determines next step |
-| 5| Submit for manager approval | Process |
-Approval action |
-| 6 | Update central database | Process | Data update operation |
-| 7 | End process | Terminator | Exit point |"</t>
-  </si>
-  <si>
-    <t>"If a structured table is provided with columns for Step No., Control Step, Risk if Missed, and Mitigatio n, clean and re-format it into a professional four-column table. Keep hyperlinks or references to step numbers accurate.
-If a paragraph is provided, extract discrete controls and rebuild them into a four-column table. Derive Logical Step No. mapping if clear.
-If blank, infer 3-5 typical controls from the procedure (Block 6) and populate each with safe, neutral draft language. Append:
-In'A Review required: control and risk points gener ated without user input.'
-Example output:
-| Step No. | Control Step | Risk if Missed | Mitigatio
-| 2 | Review client details before submission | Incorrect client data
-stored | Implement data-entry validation and peer review
-| 3 | Manager approval required | Process errors not detected | Add automated approval workflow |
-15 | System record closed properly | Incomplete documentation | Generate completion check report |
-A Review required: control and risk points generate d without user input."</t>
-  </si>
-  <si>
-    <t>Prompt: "If a structured table is provided (columns:
-Scenario, Escalate To, Timeframe, Preferred Channel), re-format it into a professional escalation matrix table. Maintain accuracy of names, roles, and timelines.
-If a paragraph is provided, extract each escalation case into table rows with the four columns mentioned above.
-If blank, infer 3-5 typical escalation scenarios from previous SOP sections (e.g., Epcedure steps, Controls &amp; Risks) and populate each with neutral placeholders. Append:
-*A Review required: escalation details generated without user input.'
-Example output:
-| Scenario / Issue | Escalate To | Timeframe |
+    <t>If provided:
+Refine the content into 1–2 concise, professional paragraphs while preserving the original meaning.
+If blank:
+Infer the process summary from uploaded transcripts, procedure steps, systems involved, reference documents, and supporting materials.
+If confidence is low:
+Insert: "Review required: Process summary could not be determined from available source materials."
+Output Requirements:
+Describe the start, key stages, and end state of the process.
+Maintain a neutral, professional tone.
+Focus on business flow rather than procedural detail.
+Avoid assumptions not supported by source materials.</t>
+  </si>
+  <si>
+    <t>If provided:
+Convert user input into a structured process-flow table.
+If blank:
+Extract the process sequence from transcripts, procedure steps, screenshots, reference documents, and supporting materials.
+If confidence is low:
+Insert: "Review required: Process flow could not be determined from available source materials."
+Output Requirements:
+Preserve the logical sequence of activities.
+Assign an appropriate flowchart shape to each action:
+Start/End → Terminator
+Action/Update/Create → Process
+Verify/Approve/Check → Decision
+Generate Document → Document
+Input/Output → Data
+Present output as a table with columns:
+Step No.
+Action
+Flowchart Shape
+Notes
+Generate as many rows as required to accurately represent the process.
+Do not invent steps unsupported by source materials.</t>
+  </si>
+  <si>
+    <t>If provided:
+Refine and standardize the controls into a structured four-column table.
+If blank:
+Identify controls, risks, validations, approvals, and checkpoints from procedure steps, transcripts, screenshots, reference documents, and supporting materials.
+If confidence is low:
+Insert: "Review required: Control points could not be determined from available source materials."
+Output Requirements:
+Present as a table with columns:
+Step No.
+Control Step
+Risk if Missed
+Mitigation
+Link controls to the most relevant procedure step where possible.
+Use concise, business-focused language.
+Do not invent regulatory or compliance requirements not supported by source materials.</t>
+  </si>
+  <si>
+    <t>If provided:
+Refine and standardize the escalation information into a structured escalation matrix.
+If blank:
+Identify escalation scenarios, ownership, timelines, and communication channels from transcripts, controls, procedure steps, reference documents, and supporting materials.
+If confidence is low:
+Insert: "Review required: Escalation details could not be determined from available source materials."
+Output Requirements:
+Present as a table with columns:
+Scenario / Issue
+Escalate To
+Timeframe
 Preferred Channel
-| Missing client data | (Pending role confirmation) |
-Within 4 hours | Teams |
-1 Approval delays | (Pending role confirmation) |
-Within 1 day | Email |
-| System outage | IT Support Team | Within 30 minutes | Ticket |
-A Review required: escalation details generated without user input."</t>
+Preserve all user-provided escalation details.
+If escalation ownership is unclear, use:
+"(Pending role confirmation)"
+Do not invent role names or organizational structures not supported by source materials.</t>
+  </si>
+  <si>
+    <t>If provided:
+Rephrase into 1–2 concise sentences while preserving the original intent.
+If blank:
+Infer the purpose from the document title, uploaded transcripts, reference documents, and supporting materials.
+If confidence is low:
+Insert: "Review required: Purpose statement could not be inferred from available source materials."
+Output Requirements:
+Use clear and professional business language.
+Focus on the objective or outcome of the process.
+Avoid implementation details or procedural steps.</t>
+  </si>
+  <si>
+    <t>If provided:
+List each applicable team, function, region, or audience clearly and consistently.
+If blank:
+Identify applicable groups from uploaded transcripts, reference documents, and supporting materials.
+If confidence is low:
+Insert: "Review required: Applicability could not be determined from available source materials."
+Output Requirements:
+Present as a bulleted list or structured table.
+Do not invent department, team, or region names.
+Only include groups explicitly referenced or strongly supported by source materials.</t>
+  </si>
+  <si>
+    <t>If provided:
+Organize the information into a two-column table with columns: System/Tool and Purpose.
+If blank:
+Identify systems, applications, platforms, or tools referenced in uploaded transcripts, screenshots, reference documents, and supporting materials.
+If confidence is low:
+Insert: "Review required: Systems involved could not be determined from available source materials."
+Output Requirements:
+Present as a table with columns: System/Tool and Purpose.
+Provide a concise purpose statement for each system identified.
+Do not invent system names that are not supported by source materials.</t>
   </si>
 </sst>
 </file>
@@ -208,20 +248,29 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -557,326 +606,307 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2E804CC-3C06-F24F-9A07-8B861F6DA1FF}">
-  <dimension ref="A1:J27"/>
+  <dimension ref="A1:M27"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A3" s="2" t="s">
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="4"/>
+      <c r="H1" s="4"/>
+      <c r="I1" s="4"/>
+      <c r="J1" s="4"/>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A3" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2" t="s">
+      <c r="B3" s="5"/>
+      <c r="C3" s="5"/>
+      <c r="D3" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2" t="s">
+      <c r="E3" s="5"/>
+      <c r="F3" s="5"/>
+      <c r="G3" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H3" s="2"/>
-      <c r="I3" s="2"/>
-      <c r="J3" s="2"/>
-    </row>
-    <row r="4" spans="1:10" ht="98" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="3" t="s">
+      <c r="H3" s="5"/>
+      <c r="I3" s="5"/>
+      <c r="J3" s="5"/>
+    </row>
+    <row r="4" spans="1:13" ht="98" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="5"/>
-      <c r="E4" s="5"/>
-      <c r="F4" s="5"/>
-      <c r="G4" s="4" t="s">
+      <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="H4" s="7"/>
+      <c r="I4" s="7"/>
+      <c r="J4" s="7"/>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A6" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="4"/>
-      <c r="I4" s="4"/>
-      <c r="J4" s="4"/>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A6" s="1" t="s">
+      <c r="B6" s="4"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4"/>
+      <c r="I6" s="4"/>
+      <c r="J6" s="4"/>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A8" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B8" s="5"/>
+      <c r="C8" s="5"/>
+      <c r="D8" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="E8" s="5"/>
+      <c r="F8" s="5"/>
+      <c r="G8" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="H8" s="5"/>
+      <c r="I8" s="5"/>
+      <c r="J8" s="5"/>
+    </row>
+    <row r="9" spans="1:13" ht="93" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
-      <c r="H6" s="1"/>
-      <c r="I6" s="1"/>
-      <c r="J6" s="1"/>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A8" s="2" t="s">
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="H9" s="7"/>
+      <c r="I9" s="7"/>
+      <c r="J9" s="7"/>
+      <c r="M9" s="6"/>
+    </row>
+    <row r="10" spans="1:13" ht="111" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
+      <c r="G10" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="H10" s="8"/>
+      <c r="I10" s="8"/>
+      <c r="J10" s="8"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A12" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B12" s="4"/>
+      <c r="C12" s="4"/>
+      <c r="D12" s="4"/>
+      <c r="E12" s="4"/>
+      <c r="F12" s="4"/>
+      <c r="G12" s="4"/>
+      <c r="H12" s="4"/>
+      <c r="I12" s="4"/>
+      <c r="J12" s="4"/>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A14" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2" t="s">
+      <c r="B14" s="5"/>
+      <c r="C14" s="5"/>
+      <c r="D14" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2" t="s">
+      <c r="E14" s="5"/>
+      <c r="F14" s="5"/>
+      <c r="G14" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H8" s="2"/>
-      <c r="I8" s="2"/>
-      <c r="J8" s="2"/>
-    </row>
-    <row r="9" spans="1:10" ht="93" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="5"/>
-      <c r="E9" s="5"/>
-      <c r="F9" s="5"/>
-      <c r="G9" s="4" t="s">
+      <c r="H14" s="5"/>
+      <c r="I14" s="5"/>
+      <c r="J14" s="5"/>
+    </row>
+    <row r="15" spans="1:13" ht="192" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B15" s="1"/>
+      <c r="C15" s="1"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
+      <c r="G15" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="H15" s="8"/>
+      <c r="I15" s="8"/>
+      <c r="J15" s="8"/>
+    </row>
+    <row r="16" spans="1:13" ht="192" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B16" s="1"/>
+      <c r="C16" s="1"/>
+      <c r="D16" s="2"/>
+      <c r="E16" s="2"/>
+      <c r="F16" s="2"/>
+      <c r="G16" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="H16" s="8"/>
+      <c r="I16" s="8"/>
+      <c r="J16" s="8"/>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A18" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B18" s="4"/>
+      <c r="C18" s="4"/>
+      <c r="D18" s="4"/>
+      <c r="E18" s="4"/>
+      <c r="F18" s="4"/>
+      <c r="G18" s="4"/>
+      <c r="H18" s="4"/>
+      <c r="I18" s="4"/>
+      <c r="J18" s="4"/>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A20" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B20" s="5"/>
+      <c r="C20" s="5"/>
+      <c r="D20" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="E20" s="5"/>
+      <c r="F20" s="5"/>
+      <c r="G20" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="H20" s="5"/>
+      <c r="I20" s="5"/>
+      <c r="J20" s="5"/>
+    </row>
+    <row r="21" spans="1:10" ht="400" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B21" s="1"/>
+      <c r="C21" s="1"/>
+      <c r="D21" s="2"/>
+      <c r="E21" s="2"/>
+      <c r="F21" s="2"/>
+      <c r="G21" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="H9" s="4"/>
-      <c r="I9" s="4"/>
-      <c r="J9" s="4"/>
-    </row>
-    <row r="10" spans="1:10" ht="111" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="5"/>
-      <c r="E10" s="5"/>
-      <c r="F10" s="5"/>
-      <c r="G10" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="H10" s="3"/>
-      <c r="I10" s="3"/>
-      <c r="J10" s="3"/>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A12" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B12" s="1"/>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="1"/>
-      <c r="F12" s="1"/>
-      <c r="G12" s="1"/>
-      <c r="H12" s="1"/>
-      <c r="I12" s="1"/>
-      <c r="J12" s="1"/>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A14" s="2" t="s">
+      <c r="H21" s="3"/>
+      <c r="I21" s="3"/>
+      <c r="J21" s="3"/>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A23" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B23" s="4"/>
+      <c r="C23" s="4"/>
+      <c r="D23" s="4"/>
+      <c r="E23" s="4"/>
+      <c r="F23" s="4"/>
+      <c r="G23" s="4"/>
+      <c r="H23" s="4"/>
+      <c r="I23" s="4"/>
+      <c r="J23" s="4"/>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A25" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2" t="s">
+      <c r="B25" s="5"/>
+      <c r="C25" s="5"/>
+      <c r="D25" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2" t="s">
+      <c r="E25" s="5"/>
+      <c r="F25" s="5"/>
+      <c r="G25" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H14" s="2"/>
-      <c r="I14" s="2"/>
-      <c r="J14" s="2"/>
-    </row>
-    <row r="15" spans="1:10" ht="192" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B15" s="3"/>
-      <c r="C15" s="3"/>
-      <c r="D15" s="5"/>
-      <c r="E15" s="5"/>
-      <c r="F15" s="5"/>
-      <c r="G15" s="4" t="s">
+      <c r="H25" s="5"/>
+      <c r="I25" s="5"/>
+      <c r="J25" s="5"/>
+    </row>
+    <row r="26" spans="1:10" ht="203" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B26" s="1"/>
+      <c r="C26" s="1"/>
+      <c r="D26" s="2"/>
+      <c r="E26" s="2"/>
+      <c r="F26" s="2"/>
+      <c r="G26" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="H26" s="8"/>
+      <c r="I26" s="8"/>
+      <c r="J26" s="8"/>
+    </row>
+    <row r="27" spans="1:10" ht="235" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B27" s="1"/>
+      <c r="C27" s="1"/>
+      <c r="D27" s="2"/>
+      <c r="E27" s="2"/>
+      <c r="F27" s="2"/>
+      <c r="G27" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="H15" s="3"/>
-      <c r="I15" s="3"/>
-      <c r="J15" s="3"/>
-    </row>
-    <row r="16" spans="1:10" ht="192" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B16" s="3"/>
-      <c r="C16" s="3"/>
-      <c r="D16" s="5"/>
-      <c r="E16" s="5"/>
-      <c r="F16" s="5"/>
-      <c r="G16" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H16" s="3"/>
-      <c r="I16" s="3"/>
-      <c r="J16" s="3"/>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A18" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B18" s="1"/>
-      <c r="C18" s="1"/>
-      <c r="D18" s="1"/>
-      <c r="E18" s="1"/>
-      <c r="F18" s="1"/>
-      <c r="G18" s="1"/>
-      <c r="H18" s="1"/>
-      <c r="I18" s="1"/>
-      <c r="J18" s="1"/>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A20" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B20" s="2"/>
-      <c r="C20" s="2"/>
-      <c r="D20" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="E20" s="2"/>
-      <c r="F20" s="2"/>
-      <c r="G20" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="H20" s="2"/>
-      <c r="I20" s="2"/>
-      <c r="J20" s="2"/>
-    </row>
-    <row r="21" spans="1:10" ht="400" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B21" s="3"/>
-      <c r="C21" s="3"/>
-      <c r="D21" s="5"/>
-      <c r="E21" s="5"/>
-      <c r="F21" s="5"/>
-      <c r="G21" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="H21" s="4"/>
-      <c r="I21" s="4"/>
-      <c r="J21" s="4"/>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A23" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B23" s="1"/>
-      <c r="C23" s="1"/>
-      <c r="D23" s="1"/>
-      <c r="E23" s="1"/>
-      <c r="F23" s="1"/>
-      <c r="G23" s="1"/>
-      <c r="H23" s="1"/>
-      <c r="I23" s="1"/>
-      <c r="J23" s="1"/>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A25" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B25" s="2"/>
-      <c r="C25" s="2"/>
-      <c r="D25" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="E25" s="2"/>
-      <c r="F25" s="2"/>
-      <c r="G25" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="H25" s="2"/>
-      <c r="I25" s="2"/>
-      <c r="J25" s="2"/>
-    </row>
-    <row r="26" spans="1:10" ht="203" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B26" s="3"/>
-      <c r="C26" s="3"/>
-      <c r="D26" s="5"/>
-      <c r="E26" s="5"/>
-      <c r="F26" s="5"/>
-      <c r="G26" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="H26" s="3"/>
-      <c r="I26" s="3"/>
-      <c r="J26" s="3"/>
-    </row>
-    <row r="27" spans="1:10" ht="235" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B27" s="3"/>
-      <c r="C27" s="3"/>
-      <c r="D27" s="5"/>
-      <c r="E27" s="5"/>
-      <c r="F27" s="5"/>
-      <c r="G27" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="H27" s="3"/>
-      <c r="I27" s="3"/>
-      <c r="J27" s="3"/>
+      <c r="H27" s="8"/>
+      <c r="I27" s="8"/>
+      <c r="J27" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="44">
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="D26:F26"/>
-    <mergeCell ref="G26:J26"/>
-    <mergeCell ref="A27:C27"/>
-    <mergeCell ref="D27:F27"/>
-    <mergeCell ref="G27:J27"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="D16:F16"/>
-    <mergeCell ref="G16:J16"/>
-    <mergeCell ref="A23:J23"/>
-    <mergeCell ref="A25:C25"/>
-    <mergeCell ref="D25:F25"/>
-    <mergeCell ref="G25:J25"/>
-    <mergeCell ref="A12:J12"/>
-    <mergeCell ref="A14:C14"/>
-    <mergeCell ref="D14:F14"/>
-    <mergeCell ref="G14:J14"/>
-    <mergeCell ref="A15:C15"/>
-    <mergeCell ref="D15:F15"/>
-    <mergeCell ref="G15:J15"/>
-    <mergeCell ref="A18:J18"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="D20:F20"/>
-    <mergeCell ref="G20:J20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="D21:F21"/>
-    <mergeCell ref="G21:J21"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="D3:F3"/>
+    <mergeCell ref="G3:J3"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="D4:F4"/>
+    <mergeCell ref="G4:J4"/>
     <mergeCell ref="A10:C10"/>
     <mergeCell ref="D10:F10"/>
     <mergeCell ref="G10:J10"/>
@@ -887,13 +917,33 @@
     <mergeCell ref="A9:C9"/>
     <mergeCell ref="D9:F9"/>
     <mergeCell ref="G9:J9"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="D3:F3"/>
-    <mergeCell ref="G3:J3"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="D4:F4"/>
-    <mergeCell ref="G4:J4"/>
+    <mergeCell ref="A12:J12"/>
+    <mergeCell ref="A14:C14"/>
+    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="G14:J14"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="G15:J15"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="G16:J16"/>
+    <mergeCell ref="A23:J23"/>
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="D25:F25"/>
+    <mergeCell ref="G25:J25"/>
+    <mergeCell ref="A18:J18"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="D20:F20"/>
+    <mergeCell ref="G20:J20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="D21:F21"/>
+    <mergeCell ref="G21:J21"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="D26:F26"/>
+    <mergeCell ref="G26:J26"/>
+    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="D27:F27"/>
+    <mergeCell ref="G27:J27"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
